--- a/Unit Test/TestPlan-EN.xlsx
+++ b/Unit Test/TestPlan-EN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Programming\ISD.ICT.20232-20215235.DinhVietQuang\Unit Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0679ED-9E4A-471E-8393-90B3B8A02966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAEF140-CD13-4F9C-B58E-0BBAC4EA4F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="540" windowWidth="18912" windowHeight="11832" firstSheet="1" activeTab="2" xr2:uid="{BA49DA37-6C72-4F0C-8F29-A460207C1BDB}"/>
+    <workbookView xWindow="2280" yWindow="408" windowWidth="18912" windowHeight="11832" xr2:uid="{BA49DA37-6C72-4F0C-8F29-A460207C1BDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
@@ -946,6 +946,9 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -973,6 +976,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -982,12 +1009,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -997,44 +1018,53 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1049,50 +1079,20 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1322,8 +1322,8 @@
       <xdr:rowOff>7471</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>597477</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>276411</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>7471</xdr:rowOff>
     </xdr:to>
@@ -1340,8 +1340,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="69272" y="3297926"/>
-          <a:ext cx="5195455" cy="1558636"/>
+          <a:off x="69272" y="3414059"/>
+          <a:ext cx="5346904" cy="1613647"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1418,19 +1418,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>XDPTPM</a:t>
+            <a:t> ITSS software development</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="2400">
             <a:solidFill>
@@ -1505,7 +1493,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="vi-VN" sz="1600">
+            <a:rPr lang="en-US" sz="1600">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1514,7 +1502,19 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Vo Hoai Nam - 20204592</a:t>
+            <a:t>Dinh</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Viet Quang - 20215235</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1600">
             <a:solidFill>
@@ -1610,43 +1610,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1600" i="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>November</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" i="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1600" i="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2023</a:t>
+            <a:t> May, 2024</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1600" i="1">
             <a:solidFill>
@@ -1980,176 +1944,176 @@
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2244,96 +2208,96 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="43"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="43"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
     </row>
     <row r="13" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -2341,116 +2305,116 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
     </row>
     <row r="15" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="44"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
+      <c r="A15" s="45"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
     </row>
     <row r="16" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="44"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
     </row>
     <row r="17" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
     </row>
     <row r="18" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
     </row>
     <row r="19" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="44"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
+      <c r="A19" s="45"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
     </row>
     <row r="22" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2468,66 +2432,66 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
     </row>
     <row r="28" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
     </row>
     <row r="29" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
     </row>
     <row r="30" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
     </row>
     <row r="31" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
     </row>
     <row r="32" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="45"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
     </row>
     <row r="33" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
@@ -2552,156 +2516,156 @@
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="46" t="s">
+      <c r="A35" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="46"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
     </row>
     <row r="38" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="46"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="46"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="46"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="46"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="46"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="46"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="46"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2736,96 +2700,96 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="47"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
+      <c r="A7" s="48"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="47"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
     </row>
     <row r="13" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
@@ -2838,56 +2802,56 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
     </row>
     <row r="16" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
     </row>
     <row r="17" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
     </row>
     <row r="18" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
     </row>
     <row r="19" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
     </row>
     <row r="20" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
@@ -2912,136 +2876,136 @@
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
     </row>
     <row r="23" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
+      <c r="A23" s="50"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
     </row>
     <row r="24" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
+      <c r="A24" s="50"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
+      <c r="A26" s="50"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
     </row>
     <row r="27" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="49"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
+      <c r="A29" s="50"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="49"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="49"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="49"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="49"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
@@ -3056,46 +3020,46 @@
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="49"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="49"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
     </row>
     <row r="38" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="49"/>
-      <c r="B38" s="49"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
+      <c r="A38" s="50"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
     </row>
     <row r="39" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="49"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
@@ -3241,216 +3205,216 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="50"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="50"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="50"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="50"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="50"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="50"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="50"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="50"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="50"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="50"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="50"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="50"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="50"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="50"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="50"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="50"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3491,11 +3455,11 @@
       <c r="B3" s="40"/>
     </row>
     <row r="4" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
       <c r="D4" s="33" t="s">
         <v>30</v>
       </c>
@@ -3788,15 +3752,15 @@
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="59" t="s">
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="G21" s="61"/>
+      <c r="G21" s="54"/>
     </row>
     <row r="22" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
@@ -3805,15 +3769,15 @@
       <c r="B22" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="54" t="s">
+      <c r="D22" s="61"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="55"/>
+      <c r="G22" s="59"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="21"/>
@@ -3836,15 +3800,15 @@
       <c r="B25" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="60"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="59" t="s">
+      <c r="D25" s="53"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="61"/>
+      <c r="G25" s="54"/>
     </row>
     <row r="26" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
@@ -3853,15 +3817,15 @@
       <c r="B26" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="52"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54" t="s">
+      <c r="D26" s="61"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="G26" s="55"/>
+      <c r="G26" s="59"/>
     </row>
     <row r="27" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
@@ -3870,15 +3834,15 @@
       <c r="B27" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="52"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="54" t="s">
+      <c r="D27" s="61"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="G27" s="55"/>
+      <c r="G27" s="59"/>
     </row>
     <row r="28" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="21"/>
@@ -3901,15 +3865,15 @@
       <c r="B30" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="59" t="s">
+      <c r="D30" s="53"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="61"/>
+      <c r="G30" s="54"/>
     </row>
     <row r="31" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
@@ -3918,24 +3882,18 @@
       <c r="B31" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="63"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="54" t="s">
+      <c r="D31" s="56"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="G31" s="55"/>
+      <c r="G31" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:G27"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="A4:C4"/>
@@ -3945,6 +3903,12 @@
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:G27"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="1.1811023622047243" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3977,17 +3941,17 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="81"/>
+      <c r="B3" s="67"/>
       <c r="C3" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="81"/>
+      <c r="E3" s="67"/>
       <c r="F3" s="24" t="s">
         <v>95</v>
       </c>
@@ -3997,21 +3961,21 @@
       <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="81"/>
+      <c r="B4" s="67"/>
       <c r="C4" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="D4" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="70" t="s">
+      <c r="E4" s="67"/>
+      <c r="F4" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="70"/>
+      <c r="G4" s="68"/>
       <c r="H4" s="26" t="s">
         <v>55</v>
       </c>
@@ -4033,10 +3997,10 @@
       <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="84"/>
+      <c r="B6" s="72"/>
       <c r="C6" s="24" t="s">
         <v>58</v>
       </c>
@@ -4061,21 +4025,21 @@
       <c r="J7" s="25"/>
     </row>
     <row r="8" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="84"/>
+      <c r="B8" s="72"/>
       <c r="C8" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="D8" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="84"/>
-      <c r="F8" s="86" t="s">
+      <c r="E8" s="72"/>
+      <c r="F8" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="87"/>
+      <c r="G8" s="75"/>
       <c r="H8" s="26" t="s">
         <v>61</v>
       </c>
@@ -4096,25 +4060,25 @@
       <c r="A10" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
     </row>
     <row r="11" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="30">
         <v>1</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
@@ -4132,15 +4096,15 @@
       <c r="A13" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79" t="s">
+      <c r="C13" s="69"/>
+      <c r="D13" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
       <c r="I13" s="25"/>
@@ -4150,11 +4114,11 @@
       <c r="A14" s="30">
         <v>1</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
       <c r="G14" s="25"/>
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
@@ -4164,11 +4128,11 @@
       <c r="A15" s="30">
         <v>2</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
@@ -4178,11 +4142,11 @@
       <c r="A16" s="30">
         <v>3</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="25"/>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
@@ -4190,21 +4154,21 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="32"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
       <c r="J17" s="24"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="71"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="24" t="s">
         <v>69</v>
       </c>
@@ -4220,82 +4184,82 @@
       <c r="C19" s="32"/>
     </row>
     <row r="20" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="74" t="s">
+      <c r="C20" s="82"/>
+      <c r="D20" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="75"/>
+      <c r="E20" s="85"/>
       <c r="F20" s="77" t="s">
         <v>73</v>
       </c>
       <c r="G20" s="77"/>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
+      <c r="A21" s="82"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
       <c r="F21" s="77"/>
       <c r="G21" s="77"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="30">
         <v>1</v>
       </c>
-      <c r="B22" s="65" t="s">
+      <c r="B22" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="65" t="s">
+      <c r="C22" s="81"/>
+      <c r="D22" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65" t="s">
+      <c r="E22" s="70"/>
+      <c r="F22" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65" t="s">
+      <c r="G22" s="70"/>
+      <c r="H22" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
     </row>
     <row r="23" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="30">
         <v>2</v>
       </c>
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="66"/>
-      <c r="D23" s="65" t="s">
+      <c r="C23" s="81"/>
+      <c r="D23" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65" t="s">
+      <c r="E23" s="70"/>
+      <c r="F23" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65" t="s">
+      <c r="G23" s="70"/>
+      <c r="H23" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
@@ -4303,17 +4267,17 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="81"/>
+      <c r="B27" s="67"/>
       <c r="C27" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="80" t="s">
+      <c r="D27" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="81"/>
+      <c r="E27" s="67"/>
       <c r="F27" s="24" t="s">
         <v>123</v>
       </c>
@@ -4323,21 +4287,21 @@
       <c r="J27" s="25"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="81"/>
+      <c r="B28" s="67"/>
       <c r="C28" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="80" t="s">
+      <c r="D28" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82" t="s">
+      <c r="E28" s="67"/>
+      <c r="F28" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="G28" s="82"/>
+      <c r="G28" s="87"/>
       <c r="H28" s="26" t="s">
         <v>55</v>
       </c>
@@ -4359,10 +4323,10 @@
       <c r="J29" s="25"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="83" t="s">
+      <c r="A30" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="84"/>
+      <c r="B30" s="72"/>
       <c r="C30" s="24"/>
       <c r="D30" s="28"/>
       <c r="E30" s="28"/>
@@ -4385,21 +4349,21 @@
       <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="85" t="s">
+      <c r="A32" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="84"/>
+      <c r="B32" s="72"/>
       <c r="C32" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="85" t="s">
+      <c r="D32" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="84"/>
-      <c r="F32" s="86" t="s">
+      <c r="E32" s="72"/>
+      <c r="F32" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="87"/>
+      <c r="G32" s="75"/>
       <c r="H32" s="26" t="s">
         <v>61</v>
       </c>
@@ -4420,25 +4384,25 @@
       <c r="A34" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="30">
         <v>1</v>
       </c>
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="25"/>
@@ -4456,15 +4420,15 @@
       <c r="A37" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="79" t="s">
+      <c r="B37" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79" t="s">
+      <c r="C37" s="69"/>
+      <c r="D37" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
       <c r="G37" s="25"/>
       <c r="H37" s="25"/>
       <c r="I37" s="25"/>
@@ -4474,11 +4438,11 @@
       <c r="A38" s="30">
         <v>1</v>
       </c>
-      <c r="B38" s="65"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
       <c r="G38" s="25"/>
       <c r="H38" s="25"/>
       <c r="I38" s="25"/>
@@ -4486,21 +4450,21 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="32"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="68"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
       <c r="I39" s="24"/>
       <c r="J39" s="24"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="71" t="s">
+      <c r="A40" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="71"/>
+      <c r="B40" s="78"/>
       <c r="C40" s="24"/>
       <c r="D40" s="25"/>
       <c r="E40" s="25"/>
@@ -4514,82 +4478,82 @@
       <c r="C41" s="32"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="69" t="s">
+      <c r="B42" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="72"/>
-      <c r="D42" s="74" t="s">
+      <c r="C42" s="82"/>
+      <c r="D42" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="E42" s="75"/>
+      <c r="E42" s="85"/>
       <c r="F42" s="77" t="s">
         <v>73</v>
       </c>
       <c r="G42" s="77"/>
-      <c r="H42" s="69" t="s">
+      <c r="H42" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="I42" s="69"/>
-      <c r="J42" s="69"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="80"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="72"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
+      <c r="A43" s="82"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
       <c r="F43" s="77"/>
       <c r="G43" s="77"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="69"/>
-      <c r="J43" s="69"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+      <c r="J43" s="80"/>
     </row>
     <row r="44" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="30">
         <v>1</v>
       </c>
-      <c r="B44" s="65" t="s">
+      <c r="B44" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="66"/>
-      <c r="D44" s="65" t="s">
+      <c r="C44" s="81"/>
+      <c r="D44" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65" t="s">
+      <c r="E44" s="70"/>
+      <c r="F44" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65" t="s">
+      <c r="G44" s="70"/>
+      <c r="H44" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
     </row>
     <row r="45" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="30">
         <v>2</v>
       </c>
-      <c r="B45" s="65" t="s">
+      <c r="B45" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="66"/>
-      <c r="D45" s="65" t="s">
+      <c r="C45" s="81"/>
+      <c r="D45" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65" t="s">
+      <c r="E45" s="70"/>
+      <c r="F45" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G45" s="65"/>
-      <c r="H45" s="65" t="s">
+      <c r="G45" s="70"/>
+      <c r="H45" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I45" s="65"/>
-      <c r="J45" s="65"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="70"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
@@ -4597,17 +4561,17 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="80" t="s">
+      <c r="A49" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="81"/>
+      <c r="B49" s="67"/>
       <c r="C49" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="80" t="s">
+      <c r="D49" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="E49" s="81"/>
+      <c r="E49" s="67"/>
       <c r="F49" s="24" t="s">
         <v>107</v>
       </c>
@@ -4617,21 +4581,21 @@
       <c r="J49" s="25"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="80" t="s">
+      <c r="A50" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="81"/>
-      <c r="C50" s="89" t="s">
+      <c r="B50" s="67"/>
+      <c r="C50" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="80" t="s">
+      <c r="D50" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E50" s="81"/>
-      <c r="F50" s="82" t="s">
+      <c r="E50" s="67"/>
+      <c r="F50" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="G50" s="82"/>
+      <c r="G50" s="87"/>
       <c r="H50" s="26" t="s">
         <v>55</v>
       </c>
@@ -4653,10 +4617,10 @@
       <c r="J51" s="25"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="84"/>
+      <c r="B52" s="72"/>
       <c r="C52" s="24"/>
       <c r="D52" s="28"/>
       <c r="E52" s="28"/>
@@ -4679,21 +4643,21 @@
       <c r="J53" s="25"/>
     </row>
     <row r="54" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="85" t="s">
+      <c r="A54" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="84"/>
-      <c r="C54" s="89" t="s">
+      <c r="B54" s="72"/>
+      <c r="C54" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D54" s="85" t="s">
+      <c r="D54" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E54" s="84"/>
-      <c r="F54" s="86" t="s">
+      <c r="E54" s="72"/>
+      <c r="F54" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="G54" s="87"/>
+      <c r="G54" s="75"/>
       <c r="H54" s="26" t="s">
         <v>61</v>
       </c>
@@ -4714,25 +4678,25 @@
       <c r="A56" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B56" s="78" t="s">
+      <c r="B56" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C56" s="78"/>
-      <c r="D56" s="78"/>
-      <c r="E56" s="78"/>
-      <c r="F56" s="78"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="76"/>
+      <c r="E56" s="76"/>
+      <c r="F56" s="76"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="30">
         <v>1</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="65"/>
-      <c r="D57" s="65"/>
-      <c r="E57" s="65"/>
-      <c r="F57" s="65"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="25"/>
@@ -4750,15 +4714,15 @@
       <c r="A59" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="79" t="s">
+      <c r="B59" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C59" s="79"/>
-      <c r="D59" s="79" t="s">
+      <c r="C59" s="69"/>
+      <c r="D59" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E59" s="79"/>
-      <c r="F59" s="79"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
       <c r="G59" s="25"/>
       <c r="H59" s="25"/>
       <c r="I59" s="25"/>
@@ -4768,15 +4732,15 @@
       <c r="A60" s="30">
         <v>1</v>
       </c>
-      <c r="B60" s="65" t="s">
+      <c r="B60" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="C60" s="65"/>
-      <c r="D60" s="65" t="s">
+      <c r="C60" s="70"/>
+      <c r="D60" s="70" t="s">
         <v>139</v>
       </c>
-      <c r="E60" s="65"/>
-      <c r="F60" s="65"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
       <c r="G60" s="25"/>
       <c r="H60" s="25"/>
       <c r="I60" s="25"/>
@@ -4786,15 +4750,15 @@
       <c r="A61" s="30">
         <v>2</v>
       </c>
-      <c r="B61" s="65" t="s">
+      <c r="B61" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="C61" s="65"/>
-      <c r="D61" s="90" t="s">
+      <c r="C61" s="70"/>
+      <c r="D61" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
       <c r="G61" s="25"/>
       <c r="H61" s="25"/>
       <c r="I61" s="25"/>
@@ -4804,15 +4768,15 @@
       <c r="A62" s="30">
         <v>3</v>
       </c>
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="C62" s="65"/>
-      <c r="D62" s="65" t="s">
+      <c r="C62" s="70"/>
+      <c r="D62" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="E62" s="65"/>
-      <c r="F62" s="65"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="70"/>
       <c r="G62" s="25"/>
       <c r="H62" s="25"/>
       <c r="I62" s="25"/>
@@ -4822,15 +4786,15 @@
       <c r="A63" s="30">
         <v>4</v>
       </c>
-      <c r="B63" s="65" t="s">
+      <c r="B63" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="65"/>
-      <c r="D63" s="65" t="s">
+      <c r="C63" s="70"/>
+      <c r="D63" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="E63" s="65"/>
-      <c r="F63" s="65"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
       <c r="G63" s="25"/>
       <c r="H63" s="25"/>
       <c r="I63" s="25"/>
@@ -4838,21 +4802,21 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="32"/>
-      <c r="B64" s="70"/>
-      <c r="C64" s="70"/>
-      <c r="D64" s="70"/>
-      <c r="E64" s="70"/>
-      <c r="F64" s="70"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="68"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
       <c r="G64" s="24"/>
       <c r="H64" s="24"/>
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="71" t="s">
+      <c r="A65" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="71"/>
+      <c r="B65" s="78"/>
       <c r="C65" s="24"/>
       <c r="D65" s="25"/>
       <c r="E65" s="25"/>
@@ -4866,104 +4830,104 @@
       <c r="C66" s="32"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="69" t="s">
+      <c r="A67" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="69" t="s">
+      <c r="B67" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="72"/>
-      <c r="D67" s="74" t="s">
+      <c r="C67" s="82"/>
+      <c r="D67" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="E67" s="75"/>
+      <c r="E67" s="85"/>
       <c r="F67" s="77" t="s">
         <v>73</v>
       </c>
       <c r="G67" s="77"/>
-      <c r="H67" s="69" t="s">
+      <c r="H67" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="I67" s="69"/>
-      <c r="J67" s="69"/>
+      <c r="I67" s="80"/>
+      <c r="J67" s="80"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="72"/>
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="76"/>
-      <c r="E68" s="76"/>
+      <c r="A68" s="82"/>
+      <c r="B68" s="83"/>
+      <c r="C68" s="83"/>
+      <c r="D68" s="86"/>
+      <c r="E68" s="86"/>
       <c r="F68" s="77"/>
       <c r="G68" s="77"/>
-      <c r="H68" s="69"/>
-      <c r="I68" s="69"/>
-      <c r="J68" s="69"/>
+      <c r="H68" s="80"/>
+      <c r="I68" s="80"/>
+      <c r="J68" s="80"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="30">
         <v>1</v>
       </c>
-      <c r="B69" s="65" t="s">
+      <c r="B69" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="66"/>
-      <c r="D69" s="65" t="s">
+      <c r="C69" s="81"/>
+      <c r="D69" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="E69" s="65"/>
-      <c r="F69" s="65" t="s">
+      <c r="E69" s="70"/>
+      <c r="F69" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G69" s="65"/>
-      <c r="H69" s="65" t="s">
+      <c r="G69" s="70"/>
+      <c r="H69" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I69" s="65"/>
-      <c r="J69" s="65"/>
+      <c r="I69" s="70"/>
+      <c r="J69" s="70"/>
     </row>
     <row r="70" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="30">
         <v>2</v>
       </c>
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="C70" s="66"/>
-      <c r="D70" s="65" t="s">
+      <c r="C70" s="81"/>
+      <c r="D70" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="E70" s="65"/>
-      <c r="F70" s="65" t="s">
+      <c r="E70" s="70"/>
+      <c r="F70" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G70" s="65"/>
-      <c r="H70" s="65" t="s">
+      <c r="G70" s="70"/>
+      <c r="H70" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I70" s="65"/>
-      <c r="J70" s="65"/>
+      <c r="I70" s="70"/>
+      <c r="J70" s="70"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="30">
         <v>3</v>
       </c>
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="C71" s="66"/>
-      <c r="D71" s="65" t="s">
+      <c r="C71" s="81"/>
+      <c r="D71" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="E71" s="65"/>
-      <c r="F71" s="65" t="s">
+      <c r="E71" s="70"/>
+      <c r="F71" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G71" s="65"/>
-      <c r="H71" s="65" t="s">
+      <c r="G71" s="70"/>
+      <c r="H71" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I71" s="65"/>
-      <c r="J71" s="65"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="70"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
@@ -4971,17 +4935,17 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="80" t="s">
+      <c r="A75" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B75" s="81"/>
+      <c r="B75" s="67"/>
       <c r="C75" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D75" s="80" t="s">
+      <c r="D75" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="E75" s="81"/>
+      <c r="E75" s="67"/>
       <c r="F75" s="24" t="s">
         <v>116</v>
       </c>
@@ -4991,21 +4955,21 @@
       <c r="J75" s="25"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="80" t="s">
+      <c r="A76" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B76" s="81"/>
-      <c r="C76" s="89" t="s">
+      <c r="B76" s="67"/>
+      <c r="C76" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D76" s="80" t="s">
+      <c r="D76" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E76" s="81"/>
-      <c r="F76" s="82" t="s">
+      <c r="E76" s="67"/>
+      <c r="F76" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="G76" s="82"/>
+      <c r="G76" s="87"/>
       <c r="H76" s="26" t="s">
         <v>55</v>
       </c>
@@ -5027,10 +4991,10 @@
       <c r="J77" s="25"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="83" t="s">
+      <c r="A78" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B78" s="84"/>
+      <c r="B78" s="72"/>
       <c r="C78" s="24"/>
       <c r="D78" s="28"/>
       <c r="E78" s="28"/>
@@ -5053,21 +5017,21 @@
       <c r="J79" s="25"/>
     </row>
     <row r="80" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="85" t="s">
+      <c r="A80" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B80" s="84"/>
-      <c r="C80" s="89" t="s">
+      <c r="B80" s="72"/>
+      <c r="C80" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D80" s="85" t="s">
+      <c r="D80" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E80" s="84"/>
-      <c r="F80" s="91" t="s">
+      <c r="E80" s="72"/>
+      <c r="F80" s="89" t="s">
         <v>140</v>
       </c>
-      <c r="G80" s="91"/>
+      <c r="G80" s="89"/>
       <c r="H80" s="26" t="s">
         <v>61</v>
       </c>
@@ -5088,25 +5052,25 @@
       <c r="A82" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B82" s="78" t="s">
+      <c r="B82" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C82" s="78"/>
-      <c r="D82" s="78"/>
-      <c r="E82" s="78"/>
-      <c r="F82" s="78"/>
+      <c r="C82" s="76"/>
+      <c r="D82" s="76"/>
+      <c r="E82" s="76"/>
+      <c r="F82" s="76"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="30">
         <v>1</v>
       </c>
-      <c r="B83" s="65" t="s">
+      <c r="B83" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="C83" s="65"/>
-      <c r="D83" s="65"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="65"/>
+      <c r="C83" s="70"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="25"/>
@@ -5124,15 +5088,15 @@
       <c r="A85" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B85" s="79" t="s">
+      <c r="B85" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79" t="s">
+      <c r="C85" s="69"/>
+      <c r="D85" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
+      <c r="E85" s="69"/>
+      <c r="F85" s="69"/>
       <c r="G85" s="25"/>
       <c r="H85" s="25"/>
       <c r="I85" s="25"/>
@@ -5142,11 +5106,11 @@
       <c r="A86" s="30">
         <v>1</v>
       </c>
-      <c r="B86" s="65"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="65"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="65"/>
+      <c r="B86" s="70"/>
+      <c r="C86" s="70"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="70"/>
       <c r="G86" s="25"/>
       <c r="H86" s="25"/>
       <c r="I86" s="25"/>
@@ -5156,11 +5120,11 @@
       <c r="A87" s="30">
         <v>2</v>
       </c>
-      <c r="B87" s="65"/>
-      <c r="C87" s="65"/>
-      <c r="D87" s="65"/>
-      <c r="E87" s="65"/>
-      <c r="F87" s="65"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="70"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="70"/>
+      <c r="F87" s="70"/>
       <c r="G87" s="25"/>
       <c r="H87" s="25"/>
       <c r="I87" s="25"/>
@@ -5170,11 +5134,11 @@
       <c r="A88" s="30">
         <v>3</v>
       </c>
-      <c r="B88" s="65"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="65"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="65"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="70"/>
+      <c r="D88" s="70"/>
+      <c r="E88" s="70"/>
+      <c r="F88" s="70"/>
       <c r="G88" s="25"/>
       <c r="H88" s="25"/>
       <c r="I88" s="25"/>
@@ -5184,11 +5148,11 @@
       <c r="A89" s="30">
         <v>4</v>
       </c>
-      <c r="B89" s="65"/>
-      <c r="C89" s="65"/>
-      <c r="D89" s="65"/>
-      <c r="E89" s="65"/>
-      <c r="F89" s="65"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="70"/>
+      <c r="D89" s="70"/>
+      <c r="E89" s="70"/>
+      <c r="F89" s="70"/>
       <c r="G89" s="25"/>
       <c r="H89" s="25"/>
       <c r="I89" s="25"/>
@@ -5196,21 +5160,21 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="32"/>
-      <c r="B90" s="70"/>
-      <c r="C90" s="70"/>
-      <c r="D90" s="70"/>
-      <c r="E90" s="70"/>
-      <c r="F90" s="70"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="68"/>
+      <c r="D90" s="68"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
       <c r="G90" s="24"/>
       <c r="H90" s="24"/>
       <c r="I90" s="24"/>
       <c r="J90" s="24"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="71" t="s">
+      <c r="A91" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B91" s="71"/>
+      <c r="B91" s="78"/>
       <c r="C91" s="24"/>
       <c r="D91" s="25"/>
       <c r="E91" s="25"/>
@@ -5224,126 +5188,126 @@
       <c r="C92" s="32"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="69" t="s">
+      <c r="A93" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B93" s="69" t="s">
+      <c r="B93" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C93" s="72"/>
-      <c r="D93" s="74" t="s">
+      <c r="C93" s="82"/>
+      <c r="D93" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="E93" s="75"/>
+      <c r="E93" s="85"/>
       <c r="F93" s="77" t="s">
         <v>73</v>
       </c>
       <c r="G93" s="77"/>
-      <c r="H93" s="69" t="s">
+      <c r="H93" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="I93" s="69"/>
-      <c r="J93" s="69"/>
+      <c r="I93" s="80"/>
+      <c r="J93" s="80"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="72"/>
-      <c r="B94" s="73"/>
-      <c r="C94" s="73"/>
-      <c r="D94" s="76"/>
-      <c r="E94" s="76"/>
+      <c r="A94" s="82"/>
+      <c r="B94" s="83"/>
+      <c r="C94" s="83"/>
+      <c r="D94" s="86"/>
+      <c r="E94" s="86"/>
       <c r="F94" s="77"/>
       <c r="G94" s="77"/>
-      <c r="H94" s="69"/>
-      <c r="I94" s="69"/>
-      <c r="J94" s="69"/>
+      <c r="H94" s="80"/>
+      <c r="I94" s="80"/>
+      <c r="J94" s="80"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="30">
         <v>1</v>
       </c>
-      <c r="B95" s="65" t="s">
+      <c r="B95" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C95" s="66"/>
-      <c r="D95" s="65" t="s">
+      <c r="C95" s="81"/>
+      <c r="D95" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="E95" s="65"/>
-      <c r="F95" s="65" t="s">
+      <c r="E95" s="70"/>
+      <c r="F95" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G95" s="65"/>
-      <c r="H95" s="65" t="s">
+      <c r="G95" s="70"/>
+      <c r="H95" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I95" s="65"/>
-      <c r="J95" s="65"/>
+      <c r="I95" s="70"/>
+      <c r="J95" s="70"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="30">
         <v>2</v>
       </c>
-      <c r="B96" s="65" t="s">
+      <c r="B96" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="C96" s="66"/>
-      <c r="D96" s="65" t="s">
+      <c r="C96" s="81"/>
+      <c r="D96" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="E96" s="65"/>
-      <c r="F96" s="65" t="s">
+      <c r="E96" s="70"/>
+      <c r="F96" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G96" s="65"/>
-      <c r="H96" s="65" t="s">
+      <c r="G96" s="70"/>
+      <c r="H96" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I96" s="65"/>
-      <c r="J96" s="65"/>
+      <c r="I96" s="70"/>
+      <c r="J96" s="70"/>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="30">
         <v>3</v>
       </c>
-      <c r="B97" s="65" t="s">
+      <c r="B97" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="C97" s="66"/>
-      <c r="D97" s="65" t="s">
+      <c r="C97" s="81"/>
+      <c r="D97" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="E97" s="65"/>
-      <c r="F97" s="67" t="s">
+      <c r="E97" s="70"/>
+      <c r="F97" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="G97" s="68"/>
-      <c r="H97" s="65" t="s">
+      <c r="G97" s="91"/>
+      <c r="H97" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I97" s="65"/>
-      <c r="J97" s="65"/>
+      <c r="I97" s="70"/>
+      <c r="J97" s="70"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="30">
         <v>4</v>
       </c>
-      <c r="B98" s="65" t="s">
+      <c r="B98" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="C98" s="66"/>
-      <c r="D98" s="65" t="s">
+      <c r="C98" s="81"/>
+      <c r="D98" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="E98" s="65"/>
-      <c r="F98" s="67" t="s">
+      <c r="E98" s="70"/>
+      <c r="F98" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="G98" s="68"/>
-      <c r="H98" s="65" t="s">
+      <c r="G98" s="91"/>
+      <c r="H98" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I98" s="65"/>
-      <c r="J98" s="65"/>
+      <c r="I98" s="70"/>
+      <c r="J98" s="70"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
@@ -5351,17 +5315,17 @@
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" s="80" t="s">
+      <c r="A102" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B102" s="81"/>
+      <c r="B102" s="67"/>
       <c r="C102" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D102" s="80" t="s">
+      <c r="D102" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="E102" s="81"/>
+      <c r="E102" s="67"/>
       <c r="F102" s="24" t="s">
         <v>120</v>
       </c>
@@ -5371,21 +5335,21 @@
       <c r="J102" s="25"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" s="80" t="s">
+      <c r="A103" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B103" s="81"/>
-      <c r="C103" s="89" t="s">
+      <c r="B103" s="67"/>
+      <c r="C103" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D103" s="80" t="s">
+      <c r="D103" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E103" s="81"/>
-      <c r="F103" s="82" t="s">
+      <c r="E103" s="67"/>
+      <c r="F103" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="G103" s="82"/>
+      <c r="G103" s="87"/>
       <c r="H103" s="26" t="s">
         <v>55</v>
       </c>
@@ -5407,10 +5371,10 @@
       <c r="J104" s="25"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A105" s="83" t="s">
+      <c r="A105" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B105" s="84"/>
+      <c r="B105" s="72"/>
       <c r="C105" s="24"/>
       <c r="D105" s="28"/>
       <c r="E105" s="28"/>
@@ -5433,21 +5397,21 @@
       <c r="J106" s="25"/>
     </row>
     <row r="107" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="85" t="s">
+      <c r="A107" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="B107" s="84"/>
-      <c r="C107" s="89" t="s">
+      <c r="B107" s="72"/>
+      <c r="C107" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="D107" s="85" t="s">
+      <c r="D107" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="E107" s="84"/>
-      <c r="F107" s="91" t="s">
+      <c r="E107" s="72"/>
+      <c r="F107" s="89" t="s">
         <v>140</v>
       </c>
-      <c r="G107" s="91"/>
+      <c r="G107" s="89"/>
       <c r="H107" s="26" t="s">
         <v>61</v>
       </c>
@@ -5468,25 +5432,25 @@
       <c r="A109" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B109" s="78" t="s">
+      <c r="B109" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C109" s="78"/>
-      <c r="D109" s="78"/>
-      <c r="E109" s="78"/>
-      <c r="F109" s="78"/>
+      <c r="C109" s="76"/>
+      <c r="D109" s="76"/>
+      <c r="E109" s="76"/>
+      <c r="F109" s="76"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="30">
         <v>1</v>
       </c>
-      <c r="B110" s="65" t="s">
+      <c r="B110" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="C110" s="65"/>
-      <c r="D110" s="65"/>
-      <c r="E110" s="65"/>
-      <c r="F110" s="65"/>
+      <c r="C110" s="70"/>
+      <c r="D110" s="70"/>
+      <c r="E110" s="70"/>
+      <c r="F110" s="70"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="25"/>
@@ -5504,15 +5468,15 @@
       <c r="A112" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B112" s="79" t="s">
+      <c r="B112" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C112" s="79"/>
-      <c r="D112" s="79" t="s">
+      <c r="C112" s="69"/>
+      <c r="D112" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E112" s="79"/>
-      <c r="F112" s="79"/>
+      <c r="E112" s="69"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="25"/>
       <c r="H112" s="25"/>
       <c r="I112" s="25"/>
@@ -5520,11 +5484,11 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="30"/>
-      <c r="B113" s="65"/>
-      <c r="C113" s="65"/>
-      <c r="D113" s="65"/>
-      <c r="E113" s="65"/>
-      <c r="F113" s="65"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="70"/>
+      <c r="D113" s="70"/>
+      <c r="E113" s="70"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="25"/>
       <c r="H113" s="25"/>
       <c r="I113" s="25"/>
@@ -5532,11 +5496,11 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="30"/>
-      <c r="B114" s="65"/>
-      <c r="C114" s="65"/>
-      <c r="D114" s="65"/>
-      <c r="E114" s="65"/>
-      <c r="F114" s="65"/>
+      <c r="B114" s="70"/>
+      <c r="C114" s="70"/>
+      <c r="D114" s="70"/>
+      <c r="E114" s="70"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="25"/>
       <c r="H114" s="25"/>
       <c r="I114" s="25"/>
@@ -5544,11 +5508,11 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="30"/>
-      <c r="B115" s="65"/>
-      <c r="C115" s="65"/>
-      <c r="D115" s="65"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="65"/>
+      <c r="B115" s="70"/>
+      <c r="C115" s="70"/>
+      <c r="D115" s="70"/>
+      <c r="E115" s="70"/>
+      <c r="F115" s="70"/>
       <c r="G115" s="25"/>
       <c r="H115" s="25"/>
       <c r="I115" s="25"/>
@@ -5556,11 +5520,11 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="30"/>
-      <c r="B116" s="65"/>
-      <c r="C116" s="65"/>
-      <c r="D116" s="65"/>
-      <c r="E116" s="65"/>
-      <c r="F116" s="65"/>
+      <c r="B116" s="70"/>
+      <c r="C116" s="70"/>
+      <c r="D116" s="70"/>
+      <c r="E116" s="70"/>
+      <c r="F116" s="70"/>
       <c r="G116" s="25"/>
       <c r="H116" s="25"/>
       <c r="I116" s="25"/>
@@ -5568,21 +5532,21 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="32"/>
-      <c r="B117" s="70"/>
-      <c r="C117" s="70"/>
-      <c r="D117" s="70"/>
-      <c r="E117" s="70"/>
-      <c r="F117" s="70"/>
+      <c r="B117" s="68"/>
+      <c r="C117" s="68"/>
+      <c r="D117" s="68"/>
+      <c r="E117" s="68"/>
+      <c r="F117" s="68"/>
       <c r="G117" s="24"/>
       <c r="H117" s="24"/>
       <c r="I117" s="24"/>
       <c r="J117" s="24"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A118" s="71" t="s">
+      <c r="A118" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B118" s="71"/>
+      <c r="B118" s="78"/>
       <c r="C118" s="24"/>
       <c r="D118" s="25"/>
       <c r="E118" s="25"/>
@@ -5596,155 +5560,276 @@
       <c r="C119" s="32"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A120" s="69" t="s">
+      <c r="A120" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="B120" s="69" t="s">
+      <c r="B120" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="C120" s="72"/>
-      <c r="D120" s="74" t="s">
+      <c r="C120" s="82"/>
+      <c r="D120" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="E120" s="75"/>
+      <c r="E120" s="85"/>
       <c r="F120" s="77" t="s">
         <v>73</v>
       </c>
       <c r="G120" s="77"/>
-      <c r="H120" s="69" t="s">
+      <c r="H120" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="I120" s="69"/>
-      <c r="J120" s="69"/>
+      <c r="I120" s="80"/>
+      <c r="J120" s="80"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A121" s="72"/>
-      <c r="B121" s="73"/>
-      <c r="C121" s="73"/>
-      <c r="D121" s="76"/>
-      <c r="E121" s="76"/>
+      <c r="A121" s="82"/>
+      <c r="B121" s="83"/>
+      <c r="C121" s="83"/>
+      <c r="D121" s="86"/>
+      <c r="E121" s="86"/>
       <c r="F121" s="77"/>
       <c r="G121" s="77"/>
-      <c r="H121" s="69"/>
-      <c r="I121" s="69"/>
-      <c r="J121" s="69"/>
+      <c r="H121" s="80"/>
+      <c r="I121" s="80"/>
+      <c r="J121" s="80"/>
     </row>
     <row r="122" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="30">
         <v>1</v>
       </c>
-      <c r="B122" s="65" t="s">
+      <c r="B122" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="C122" s="66"/>
-      <c r="D122" s="65" t="s">
+      <c r="C122" s="81"/>
+      <c r="D122" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="E122" s="65"/>
-      <c r="F122" s="65" t="s">
+      <c r="E122" s="70"/>
+      <c r="F122" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G122" s="65"/>
-      <c r="H122" s="65" t="s">
+      <c r="G122" s="70"/>
+      <c r="H122" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I122" s="65"/>
-      <c r="J122" s="65"/>
+      <c r="I122" s="70"/>
+      <c r="J122" s="70"/>
     </row>
     <row r="123" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="30">
         <v>2</v>
       </c>
-      <c r="B123" s="65" t="s">
+      <c r="B123" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="C123" s="66"/>
-      <c r="D123" s="65" t="s">
+      <c r="C123" s="81"/>
+      <c r="D123" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="E123" s="65"/>
-      <c r="F123" s="65" t="s">
+      <c r="E123" s="70"/>
+      <c r="F123" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G123" s="65"/>
-      <c r="H123" s="65" t="s">
+      <c r="G123" s="70"/>
+      <c r="H123" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I123" s="65"/>
-      <c r="J123" s="65"/>
+      <c r="I123" s="70"/>
+      <c r="J123" s="70"/>
     </row>
     <row r="124" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="30">
         <v>3</v>
       </c>
-      <c r="B124" s="65" t="s">
+      <c r="B124" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="C124" s="66"/>
-      <c r="D124" s="65" t="s">
+      <c r="C124" s="81"/>
+      <c r="D124" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="E124" s="65"/>
-      <c r="F124" s="65" t="s">
+      <c r="E124" s="70"/>
+      <c r="F124" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G124" s="65"/>
-      <c r="H124" s="65" t="s">
+      <c r="G124" s="70"/>
+      <c r="H124" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I124" s="65"/>
-      <c r="J124" s="65"/>
+      <c r="I124" s="70"/>
+      <c r="J124" s="70"/>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="30">
         <v>4</v>
       </c>
-      <c r="B125" s="65" t="s">
+      <c r="B125" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="C125" s="66"/>
-      <c r="D125" s="65" t="s">
+      <c r="C125" s="81"/>
+      <c r="D125" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="E125" s="65"/>
-      <c r="F125" s="65" t="s">
+      <c r="E125" s="70"/>
+      <c r="F125" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G125" s="65"/>
-      <c r="H125" s="65" t="s">
+      <c r="G125" s="70"/>
+      <c r="H125" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="I125" s="65"/>
-      <c r="J125" s="65"/>
+      <c r="I125" s="70"/>
+      <c r="J125" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F20:G21"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="H125:J125"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:E124"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="H124:J124"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="H98:J98"/>
+    <mergeCell ref="H120:J121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:E123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="H123:J123"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:C121"/>
+    <mergeCell ref="D120:E121"/>
+    <mergeCell ref="F120:G121"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="H97:J97"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="H93:J94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="H96:J96"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:C94"/>
+    <mergeCell ref="D93:E94"/>
+    <mergeCell ref="F93:G94"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="H70:J70"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:C68"/>
+    <mergeCell ref="D67:E68"/>
+    <mergeCell ref="F67:G68"/>
+    <mergeCell ref="H67:J68"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="D42:E43"/>
+    <mergeCell ref="F42:G43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="H42:J43"/>
     <mergeCell ref="H20:J21"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="D44:E44"/>
@@ -5769,153 +5854,32 @@
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="H42:J43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="D42:E43"/>
-    <mergeCell ref="F42:G43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="H69:J69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="H70:J70"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:C68"/>
-    <mergeCell ref="D67:E68"/>
-    <mergeCell ref="F67:G68"/>
-    <mergeCell ref="H67:J68"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:C94"/>
-    <mergeCell ref="D93:E94"/>
-    <mergeCell ref="F93:G94"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="H97:J97"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="H93:J94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="D96:E96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="H96:J96"/>
-    <mergeCell ref="B109:F109"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="D107:E107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="B120:C121"/>
-    <mergeCell ref="D120:E121"/>
-    <mergeCell ref="F120:G121"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="D125:E125"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="H125:J125"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="D124:E124"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="H124:J124"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="D98:E98"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="H98:J98"/>
-    <mergeCell ref="H120:J121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="D123:E123"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="H123:J123"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F20:G21"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <pageMargins left="1.1811023622047245" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -5923,6 +5887,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D27483CF1B63FA4AA03D15E9EA85AD57" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dc40f05d5172330021a6e9de5317fd1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c078926d-f3db-4b74-bbd0-f33b483d4b1e" xmlns:ns4="806a97cf-37b5-43d8-9f6a-27e74bb9243f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e98100bc02576a7c959853f71e43f81a" ns3:_="" ns4:_="">
     <xsd:import namespace="c078926d-f3db-4b74-bbd0-f33b483d4b1e"/>
@@ -6139,12 +6109,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6155,6 +6119,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8655864D-7A2A-4402-AA52-01C6DA779FC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E2B2261-6191-43A6-8C41-B739157DC3A6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6173,15 +6146,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8655864D-7A2A-4402-AA52-01C6DA779FC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6913AF88-A569-4E93-8BD1-0040FA9C021A}">
   <ds:schemaRefs>
